--- a/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/coercion_wave1/SCN-EB025-FUNCTION-CORE.xlsx
+++ b/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/coercion_wave1/SCN-EB025-FUNCTION-CORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260228-180047-excel-compat-empirical-pass-01\fixtures\coercion_wave1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDA90F7-A115-4C34-B08D-643B9C574465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27C2D16-2920-4C6E-A89E-EDFD1A6040C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="3075" windowWidth="17460" windowHeight="11595" xr2:uid="{896577AF-9F5E-44F7-B4C3-F76B9AFD3FA6}"/>
+    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{6CEFF41D-5CB6-46C1-8610-3EFC0FB9A017}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -401,7 +401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87395930-F24E-4340-AB6C-F81D1FF4F989}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065EE39A-8E76-4F30-BCF2-6568945AC5EF}">
   <dimension ref="B1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
